--- a/excel/common.xlsx
+++ b/excel/common.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -508,6 +508,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -520,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -574,6 +579,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -602,6 +612,7 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -630,6 +641,7 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -658,6 +670,7 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -690,6 +703,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -722,6 +740,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -754,6 +777,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -786,6 +814,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -818,6 +847,7 @@
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -850,6 +880,7 @@
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -882,6 +913,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -914,6 +946,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -946,6 +979,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -978,6 +1012,7 @@
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -990,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -1044,6 +1079,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1076,6 +1116,11 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1088,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -1142,6 +1187,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1170,6 +1220,11 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1202,6 +1257,11 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1234,6 +1294,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1266,6 +1331,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1294,6 +1364,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1326,6 +1401,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1358,6 +1438,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1390,6 +1475,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1402,7 +1492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -1456,6 +1546,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1484,6 +1579,11 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1512,6 +1612,11 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1540,6 +1645,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1568,6 +1678,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1596,6 +1711,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1624,6 +1744,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1652,6 +1777,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1680,6 +1810,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1692,7 +1827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -1746,6 +1881,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1758,7 +1898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -1812,6 +1952,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1840,6 +1985,11 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1868,6 +2018,11 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1900,6 +2055,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1932,6 +2092,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>transformer-1@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1960,6 +2125,7 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1988,6 +2154,7 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2016,6 +2183,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
